--- a/docs/ig/CodeSystem-dipag-rechnungsstatus-cs.xlsx
+++ b/docs/ig/CodeSystem-dipag-rechnungsstatus-cs.xlsx
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>CodeSystem für die Abbildung von verschieden Status eines Rechnungungsdokuments</t>
+    <t>CodeSystem für die Abbildung der verschiedenen Bearbeitungsstatus eines Rechnungsdokuments</t>
   </si>
   <si>
     <t>Purpose</t>
